--- a/backtest_runs/20260410_193731/by_symbol/AMBL/AMBL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/AMBL/AMBL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-418.9000000000059</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>108461.78</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>108461.78</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>108461.78</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>108461.78</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>108461.78</v>
@@ -1093,7 +1093,7 @@
         <v>-3853.880000000007</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>109676.59</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>109676.59</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>109676.59</v>
@@ -1461,7 +1461,7 @@
         <v>-7163.190000000003</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>107749.65</v>
@@ -1599,7 +1599,7 @@
         <v>-3476.869999999993</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>104272.78</v>
@@ -1645,7 +1645,7 @@
         <v>-2806.630000000007</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>101466.15</v>
